--- a/6 term/СА/lab2/lab2.xlsx
+++ b/6 term/СА/lab2/lab2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\atyme\OneDrive\Документы\GitHub\BSUIR-labs\6 term\СА\lab2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67FB1497-42FA-455B-BC25-C10C806FCFA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A43C93AE-C725-487A-8FAB-A82D31398E9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="170" yWindow="190" windowWidth="13080" windowHeight="15280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист2" sheetId="3" r:id="rId1"/>
@@ -328,24 +328,6 @@
     <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -367,14 +349,8 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -389,9 +365,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -408,6 +381,33 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -730,42 +730,42 @@
   </cols>
   <sheetData>
     <row r="6" spans="1:30" x14ac:dyDescent="0.35">
-      <c r="P6" s="32" t="s">
+      <c r="P6" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="Q6" s="32"/>
-      <c r="R6" s="32" t="s">
+      <c r="Q6" s="40"/>
+      <c r="R6" s="40" t="s">
         <v>48</v>
       </c>
-      <c r="S6" s="32"/>
-      <c r="T6" s="33"/>
-      <c r="U6" s="33"/>
-      <c r="V6" s="33"/>
-      <c r="W6" s="33"/>
-      <c r="X6" s="33"/>
-      <c r="Y6" s="33"/>
-      <c r="Z6" s="33"/>
-      <c r="AA6" s="33"/>
-      <c r="AB6" s="33"/>
-      <c r="AC6" s="33"/>
-      <c r="AD6" s="33"/>
+      <c r="S6" s="40"/>
+      <c r="T6" s="25"/>
+      <c r="U6" s="25"/>
+      <c r="V6" s="25"/>
+      <c r="W6" s="25"/>
+      <c r="X6" s="25"/>
+      <c r="Y6" s="25"/>
+      <c r="Z6" s="25"/>
+      <c r="AA6" s="25"/>
+      <c r="AB6" s="25"/>
+      <c r="AC6" s="25"/>
+      <c r="AD6" s="25"/>
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.35">
-      <c r="P7" s="33"/>
-      <c r="Q7" s="33"/>
-      <c r="R7" s="33"/>
-      <c r="S7" s="33"/>
-      <c r="T7" s="33"/>
-      <c r="U7" s="33"/>
-      <c r="V7" s="33"/>
-      <c r="W7" s="33"/>
-      <c r="X7" s="33"/>
-      <c r="Y7" s="33"/>
-      <c r="Z7" s="33"/>
-      <c r="AA7" s="33"/>
-      <c r="AB7" s="33"/>
-      <c r="AC7" s="33"/>
-      <c r="AD7" s="33"/>
+      <c r="P7" s="25"/>
+      <c r="Q7" s="25"/>
+      <c r="R7" s="25"/>
+      <c r="S7" s="25"/>
+      <c r="T7" s="25"/>
+      <c r="U7" s="25"/>
+      <c r="V7" s="25"/>
+      <c r="W7" s="25"/>
+      <c r="X7" s="25"/>
+      <c r="Y7" s="25"/>
+      <c r="Z7" s="25"/>
+      <c r="AA7" s="25"/>
+      <c r="AB7" s="25"/>
+      <c r="AC7" s="25"/>
+      <c r="AD7" s="25"/>
     </row>
     <row r="8" spans="1:30" x14ac:dyDescent="0.35">
       <c r="E8" s="8"/>
@@ -788,53 +788,53 @@
       <c r="M8" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="P8" s="33" t="s">
+      <c r="P8" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="Q8" s="34">
+      <c r="Q8" s="26">
         <f>SUM(F9:F11)</f>
         <v>1.3428571428571427</v>
       </c>
-      <c r="R8" s="33"/>
-      <c r="S8" s="33"/>
-      <c r="T8" s="35" t="s">
+      <c r="R8" s="25"/>
+      <c r="S8" s="25"/>
+      <c r="T8" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="U8" s="36">
+      <c r="U8" s="28">
         <f>Q8*F20+Q9*F21+Q10*F22</f>
         <v>3.0648875798728188</v>
       </c>
-      <c r="V8" s="33"/>
-      <c r="W8" s="37" t="s">
+      <c r="V8" s="25"/>
+      <c r="W8" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="X8" s="36">
+      <c r="X8" s="28">
         <f>(U8-3)/(3-1)</f>
         <v>3.2443789936409395E-2</v>
       </c>
-      <c r="Y8" s="33"/>
-      <c r="Z8" s="37" t="s">
+      <c r="Y8" s="25"/>
+      <c r="Z8" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="AA8" s="38">
+      <c r="AA8" s="30">
         <v>0.57999999999999996</v>
       </c>
-      <c r="AB8" s="33"/>
-      <c r="AC8" s="37" t="s">
+      <c r="AB8" s="25"/>
+      <c r="AC8" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="AD8" s="36">
+      <c r="AD8" s="28">
         <f>X8/AA8</f>
         <v>5.5937568855878271E-2</v>
       </c>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.35">
-      <c r="A9" s="18" t="s">
+      <c r="A9" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="B9" s="18"/>
-      <c r="C9" s="18"/>
-      <c r="D9" s="19"/>
+      <c r="B9" s="44"/>
+      <c r="C9" s="44"/>
+      <c r="D9" s="45"/>
       <c r="E9" s="8" t="s">
         <v>0</v>
       </c>
@@ -859,34 +859,34 @@
       <c r="M9" s="9">
         <v>5</v>
       </c>
-      <c r="P9" s="33" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q9" s="34">
+      <c r="P9" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="26">
         <f>SUM(G9:G11)</f>
         <v>6.333333333333333</v>
       </c>
-      <c r="R9" s="33"/>
-      <c r="S9" s="33"/>
-      <c r="T9" s="33"/>
-      <c r="U9" s="33"/>
-      <c r="V9" s="33"/>
-      <c r="W9" s="33"/>
-      <c r="X9" s="33"/>
-      <c r="Y9" s="33"/>
-      <c r="Z9" s="33"/>
-      <c r="AA9" s="33"/>
-      <c r="AB9" s="33"/>
-      <c r="AC9" s="33"/>
-      <c r="AD9" s="33"/>
+      <c r="R9" s="25"/>
+      <c r="S9" s="25"/>
+      <c r="T9" s="25"/>
+      <c r="U9" s="25"/>
+      <c r="V9" s="25"/>
+      <c r="W9" s="25"/>
+      <c r="X9" s="25"/>
+      <c r="Y9" s="25"/>
+      <c r="Z9" s="25"/>
+      <c r="AA9" s="25"/>
+      <c r="AB9" s="25"/>
+      <c r="AC9" s="25"/>
+      <c r="AD9" s="25"/>
     </row>
     <row r="10" spans="1:30" x14ac:dyDescent="0.35">
-      <c r="A10" s="18" t="s">
+      <c r="A10" s="44" t="s">
         <v>35</v>
       </c>
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="19"/>
+      <c r="B10" s="44"/>
+      <c r="C10" s="44"/>
+      <c r="D10" s="45"/>
       <c r="E10" s="8" t="s">
         <v>1</v>
       </c>
@@ -911,34 +911,34 @@
       <c r="M10" s="8">
         <v>0.33333333333333331</v>
       </c>
-      <c r="P10" s="33" t="s">
+      <c r="P10" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="Q10" s="34">
+      <c r="Q10" s="26">
         <f>SUM(H9:H11)</f>
         <v>11</v>
       </c>
-      <c r="R10" s="33"/>
-      <c r="S10" s="33"/>
-      <c r="T10" s="33"/>
-      <c r="U10" s="33"/>
-      <c r="V10" s="33"/>
-      <c r="W10" s="33"/>
-      <c r="X10" s="33"/>
-      <c r="Y10" s="33"/>
-      <c r="Z10" s="33"/>
-      <c r="AA10" s="33"/>
-      <c r="AB10" s="33"/>
-      <c r="AC10" s="33"/>
-      <c r="AD10" s="33"/>
+      <c r="R10" s="25"/>
+      <c r="S10" s="25"/>
+      <c r="T10" s="25"/>
+      <c r="U10" s="25"/>
+      <c r="V10" s="25"/>
+      <c r="W10" s="25"/>
+      <c r="X10" s="25"/>
+      <c r="Y10" s="25"/>
+      <c r="Z10" s="25"/>
+      <c r="AA10" s="25"/>
+      <c r="AB10" s="25"/>
+      <c r="AC10" s="25"/>
+      <c r="AD10" s="25"/>
     </row>
     <row r="11" spans="1:30" x14ac:dyDescent="0.35">
-      <c r="A11" s="20" t="s">
+      <c r="A11" s="46" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="20"/>
-      <c r="C11" s="20"/>
-      <c r="D11" s="21"/>
+      <c r="B11" s="46"/>
+      <c r="C11" s="46"/>
+      <c r="D11" s="47"/>
       <c r="E11" s="8" t="s">
         <v>2</v>
       </c>
@@ -970,33 +970,33 @@
       <c r="C12" s="14"/>
     </row>
     <row r="13" spans="1:30" x14ac:dyDescent="0.35">
-      <c r="E13" s="17" t="s">
+      <c r="E13" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="F13" s="17"/>
-      <c r="J13" s="17" t="s">
+      <c r="F13" s="43"/>
+      <c r="J13" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="K13" s="17"/>
-      <c r="P13" s="39" t="s">
+      <c r="K13" s="43"/>
+      <c r="P13" s="41" t="s">
         <v>41</v>
       </c>
-      <c r="Q13" s="39"/>
-      <c r="R13" s="39" t="s">
+      <c r="Q13" s="41"/>
+      <c r="R13" s="41" t="s">
         <v>47</v>
       </c>
-      <c r="S13" s="39"/>
-      <c r="T13" s="40"/>
-      <c r="U13" s="40"/>
-      <c r="V13" s="40"/>
-      <c r="W13" s="40"/>
-      <c r="X13" s="40"/>
-      <c r="Y13" s="40"/>
-      <c r="Z13" s="40"/>
-      <c r="AA13" s="40"/>
-      <c r="AB13" s="40"/>
-      <c r="AC13" s="40"/>
-      <c r="AD13" s="40"/>
+      <c r="S13" s="41"/>
+      <c r="T13" s="31"/>
+      <c r="U13" s="31"/>
+      <c r="V13" s="31"/>
+      <c r="W13" s="31"/>
+      <c r="X13" s="31"/>
+      <c r="Y13" s="31"/>
+      <c r="Z13" s="31"/>
+      <c r="AA13" s="31"/>
+      <c r="AB13" s="31"/>
+      <c r="AC13" s="31"/>
+      <c r="AD13" s="31"/>
     </row>
     <row r="14" spans="1:30" x14ac:dyDescent="0.35">
       <c r="E14" s="10" t="s">
@@ -1013,21 +1013,21 @@
         <f>GEOMEAN(K9:M9)</f>
         <v>3.2710663101885897</v>
       </c>
-      <c r="P14" s="40"/>
-      <c r="Q14" s="40"/>
-      <c r="R14" s="40"/>
-      <c r="S14" s="40"/>
-      <c r="T14" s="40"/>
-      <c r="U14" s="40"/>
-      <c r="V14" s="40"/>
-      <c r="W14" s="40"/>
-      <c r="X14" s="40"/>
-      <c r="Y14" s="40"/>
-      <c r="Z14" s="40"/>
-      <c r="AA14" s="40"/>
-      <c r="AB14" s="40"/>
-      <c r="AC14" s="40"/>
-      <c r="AD14" s="40"/>
+      <c r="P14" s="31"/>
+      <c r="Q14" s="31"/>
+      <c r="R14" s="31"/>
+      <c r="S14" s="31"/>
+      <c r="T14" s="31"/>
+      <c r="U14" s="31"/>
+      <c r="V14" s="31"/>
+      <c r="W14" s="31"/>
+      <c r="X14" s="31"/>
+      <c r="Y14" s="31"/>
+      <c r="Z14" s="31"/>
+      <c r="AA14" s="31"/>
+      <c r="AB14" s="31"/>
+      <c r="AC14" s="31"/>
+      <c r="AD14" s="31"/>
     </row>
     <row r="15" spans="1:30" x14ac:dyDescent="0.35">
       <c r="E15" s="10" t="s">
@@ -1044,42 +1044,42 @@
         <f>GEOMEAN(K10:M10)</f>
         <v>0.36246012433429736</v>
       </c>
-      <c r="P15" s="40" t="s">
+      <c r="P15" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="Q15" s="41">
+      <c r="Q15" s="32">
         <f>SUM(K9:K11)</f>
         <v>1.3428571428571427</v>
       </c>
-      <c r="R15" s="40"/>
-      <c r="S15" s="40"/>
-      <c r="T15" s="42" t="s">
+      <c r="R15" s="31"/>
+      <c r="S15" s="31"/>
+      <c r="T15" s="33" t="s">
         <v>42</v>
       </c>
-      <c r="U15" s="43">
+      <c r="U15" s="34">
         <f>Q15*K20+Q16*K21+Q17*K22</f>
         <v>3.0648875798728188</v>
       </c>
-      <c r="V15" s="40"/>
-      <c r="W15" s="44" t="s">
+      <c r="V15" s="31"/>
+      <c r="W15" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="X15" s="43">
+      <c r="X15" s="34">
         <f>(U15-3)/(3-1)</f>
         <v>3.2443789936409395E-2</v>
       </c>
-      <c r="Y15" s="40"/>
-      <c r="Z15" s="44" t="s">
+      <c r="Y15" s="31"/>
+      <c r="Z15" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="AA15" s="45">
+      <c r="AA15" s="36">
         <v>0.57999999999999996</v>
       </c>
-      <c r="AB15" s="40"/>
-      <c r="AC15" s="44" t="s">
+      <c r="AB15" s="31"/>
+      <c r="AC15" s="35" t="s">
         <v>45</v>
       </c>
-      <c r="AD15" s="43">
+      <c r="AD15" s="34">
         <f>X15/AA15</f>
         <v>5.5937568855878271E-2</v>
       </c>
@@ -1099,26 +1099,26 @@
         <f>GEOMEAN(K11:M11)</f>
         <v>0.84343266530174932</v>
       </c>
-      <c r="P16" s="40" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q16" s="41">
+      <c r="P16" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q16" s="32">
         <f>SUM(L9:L11)</f>
         <v>11</v>
       </c>
-      <c r="R16" s="40"/>
-      <c r="S16" s="40"/>
-      <c r="T16" s="40"/>
-      <c r="U16" s="40"/>
-      <c r="V16" s="40"/>
-      <c r="W16" s="40"/>
-      <c r="X16" s="40"/>
-      <c r="Y16" s="40"/>
-      <c r="Z16" s="40"/>
-      <c r="AA16" s="40"/>
-      <c r="AB16" s="40"/>
-      <c r="AC16" s="40"/>
-      <c r="AD16" s="40"/>
+      <c r="R16" s="31"/>
+      <c r="S16" s="31"/>
+      <c r="T16" s="31"/>
+      <c r="U16" s="31"/>
+      <c r="V16" s="31"/>
+      <c r="W16" s="31"/>
+      <c r="X16" s="31"/>
+      <c r="Y16" s="31"/>
+      <c r="Z16" s="31"/>
+      <c r="AA16" s="31"/>
+      <c r="AB16" s="31"/>
+      <c r="AC16" s="31"/>
+      <c r="AD16" s="31"/>
     </row>
     <row r="17" spans="4:32" x14ac:dyDescent="0.35">
       <c r="E17" s="10" t="s">
@@ -1135,36 +1135,36 @@
         <f>SUM(K13:K16)</f>
         <v>4.4769590998246365</v>
       </c>
-      <c r="P17" s="40" t="s">
+      <c r="P17" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="Q17" s="41">
+      <c r="Q17" s="32">
         <f>SUM(M9:M11)</f>
         <v>6.333333333333333</v>
       </c>
-      <c r="R17" s="40"/>
-      <c r="S17" s="40"/>
-      <c r="T17" s="40"/>
-      <c r="U17" s="40"/>
-      <c r="V17" s="40"/>
-      <c r="W17" s="40"/>
-      <c r="X17" s="40"/>
-      <c r="Y17" s="40"/>
-      <c r="Z17" s="40"/>
-      <c r="AA17" s="40"/>
-      <c r="AB17" s="40"/>
-      <c r="AC17" s="40"/>
-      <c r="AD17" s="40"/>
+      <c r="R17" s="31"/>
+      <c r="S17" s="31"/>
+      <c r="T17" s="31"/>
+      <c r="U17" s="31"/>
+      <c r="V17" s="31"/>
+      <c r="W17" s="31"/>
+      <c r="X17" s="31"/>
+      <c r="Y17" s="31"/>
+      <c r="Z17" s="31"/>
+      <c r="AA17" s="31"/>
+      <c r="AB17" s="31"/>
+      <c r="AC17" s="31"/>
+      <c r="AD17" s="31"/>
     </row>
     <row r="19" spans="4:32" x14ac:dyDescent="0.35">
-      <c r="E19" s="17" t="s">
+      <c r="E19" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="F19" s="17"/>
-      <c r="J19" s="17" t="s">
+      <c r="F19" s="43"/>
+      <c r="J19" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="K19" s="17"/>
+      <c r="K19" s="43"/>
     </row>
     <row r="20" spans="4:32" x14ac:dyDescent="0.35">
       <c r="E20" s="4" t="s">
@@ -1215,30 +1215,30 @@
       </c>
     </row>
     <row r="27" spans="4:32" x14ac:dyDescent="0.35">
-      <c r="E27" s="16" t="s">
+      <c r="E27" s="42" t="s">
         <v>39</v>
       </c>
-      <c r="F27" s="16"/>
-      <c r="G27" s="16"/>
-      <c r="H27" s="16"/>
-      <c r="I27" s="16"/>
-      <c r="J27" s="16"/>
-      <c r="L27" s="16" t="s">
+      <c r="F27" s="42"/>
+      <c r="G27" s="42"/>
+      <c r="H27" s="42"/>
+      <c r="I27" s="42"/>
+      <c r="J27" s="42"/>
+      <c r="L27" s="42" t="s">
         <v>33</v>
       </c>
-      <c r="M27" s="16"/>
-      <c r="N27" s="16"/>
-      <c r="O27" s="16"/>
-      <c r="P27" s="16"/>
-      <c r="Q27" s="16"/>
-      <c r="T27" s="28" t="s">
+      <c r="M27" s="42"/>
+      <c r="N27" s="42"/>
+      <c r="O27" s="42"/>
+      <c r="P27" s="42"/>
+      <c r="Q27" s="42"/>
+      <c r="T27" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="U27" s="28"/>
-      <c r="V27" s="28"/>
-      <c r="W27" s="28"/>
-      <c r="X27" s="28"/>
-      <c r="Y27" s="28"/>
+      <c r="U27" s="22"/>
+      <c r="V27" s="22"/>
+      <c r="W27" s="22"/>
+      <c r="X27" s="22"/>
+      <c r="Y27" s="22"/>
     </row>
     <row r="28" spans="4:32" x14ac:dyDescent="0.35">
       <c r="D28" s="7"/>
@@ -1298,14 +1298,14 @@
       <c r="Z28" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="AB28" s="17" t="s">
+      <c r="AB28" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="AC28" s="17"/>
-      <c r="AE28" s="17" t="s">
+      <c r="AC28" s="43"/>
+      <c r="AE28" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="AF28" s="17"/>
+      <c r="AF28" s="43"/>
     </row>
     <row r="29" spans="4:32" x14ac:dyDescent="0.35">
       <c r="D29" s="7" t="s">
@@ -1314,7 +1314,7 @@
       <c r="E29" s="9">
         <v>1</v>
       </c>
-      <c r="F29" s="25">
+      <c r="F29" s="19">
         <v>0.5</v>
       </c>
       <c r="G29" s="9">
@@ -1382,7 +1382,7 @@
         <v>40</v>
       </c>
       <c r="AF29" s="12">
-        <f>I37*$K$20+P37*$K$21+W37*$K$22</f>
+        <f t="shared" ref="AF29:AF34" si="0">I37*$K$20+P37*$K$21+W37*$K$22</f>
         <v>0.14252425514654499</v>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="E30" s="9">
         <v>2</v>
       </c>
-      <c r="F30" s="26">
+      <c r="F30" s="20">
         <v>1</v>
       </c>
       <c r="G30" s="9">
@@ -1461,7 +1461,7 @@
         <v>20</v>
       </c>
       <c r="AF30" s="12">
-        <f>I38*$K$20+P38*$K$21+W38*$K$22</f>
+        <f t="shared" si="0"/>
         <v>0.23293588890828282</v>
       </c>
     </row>
@@ -1472,7 +1472,7 @@
       <c r="E31" s="8">
         <v>0.25</v>
       </c>
-      <c r="F31" s="27">
+      <c r="F31" s="21">
         <v>0.2</v>
       </c>
       <c r="G31" s="9">
@@ -1540,7 +1540,7 @@
         <v>21</v>
       </c>
       <c r="AF31" s="12">
-        <f>I39*$K$20+P39*$K$21+W39*$K$22</f>
+        <f t="shared" si="0"/>
         <v>9.4289666669478939E-2</v>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
       <c r="E32" s="9">
         <v>3</v>
       </c>
-      <c r="F32" s="26">
+      <c r="F32" s="20">
         <v>2</v>
       </c>
       <c r="G32" s="9">
@@ -1619,7 +1619,7 @@
         <v>22</v>
       </c>
       <c r="AF32" s="12">
-        <f>I40*$K$20+P40*$K$21+W40*$K$22</f>
+        <f t="shared" si="0"/>
         <v>0.26156261177482559</v>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       <c r="E33" s="9">
         <v>2</v>
       </c>
-      <c r="F33" s="26">
+      <c r="F33" s="20">
         <v>1</v>
       </c>
       <c r="G33" s="9">
@@ -1698,7 +1698,7 @@
         <v>23</v>
       </c>
       <c r="AF33" s="12">
-        <f>I41*$K$20+P41*$K$21+W41*$K$22</f>
+        <f t="shared" si="0"/>
         <v>0.196434639607801</v>
       </c>
     </row>
@@ -1709,7 +1709,7 @@
       <c r="E34" s="9">
         <v>1</v>
       </c>
-      <c r="F34" s="27">
+      <c r="F34" s="21">
         <v>0.5</v>
       </c>
       <c r="G34" s="9">
@@ -1777,7 +1777,7 @@
         <v>24</v>
       </c>
       <c r="AF34" s="12">
-        <f>I42*$K$20+P42*$K$21+W42*$K$22</f>
+        <f t="shared" si="0"/>
         <v>0.13170560143872059</v>
       </c>
     </row>
@@ -1796,37 +1796,37 @@
       </c>
     </row>
     <row r="36" spans="4:32" x14ac:dyDescent="0.35">
-      <c r="E36" s="17" t="s">
+      <c r="E36" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="F36" s="17"/>
-      <c r="H36" s="17" t="s">
+      <c r="F36" s="43"/>
+      <c r="H36" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="I36" s="17"/>
-      <c r="L36" s="17" t="s">
+      <c r="I36" s="43"/>
+      <c r="L36" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="M36" s="17"/>
-      <c r="O36" s="17" t="s">
+      <c r="M36" s="43"/>
+      <c r="O36" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="P36" s="17"/>
-      <c r="S36" s="17" t="s">
+      <c r="P36" s="43"/>
+      <c r="S36" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="T36" s="17"/>
-      <c r="V36" s="17" t="s">
+      <c r="T36" s="43"/>
+      <c r="V36" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="W36" s="17"/>
+      <c r="W36" s="43"/>
     </row>
     <row r="37" spans="4:32" x14ac:dyDescent="0.35">
       <c r="E37" s="10" t="s">
         <v>3</v>
       </c>
       <c r="F37" s="12">
-        <f>GEOMEAN(E29:J29)</f>
+        <f t="shared" ref="F37:F42" si="1">GEOMEAN(E29:J29)</f>
         <v>0.83268317765560429</v>
       </c>
       <c r="H37" s="10" t="s">
@@ -1840,7 +1840,7 @@
         <v>3</v>
       </c>
       <c r="M37" s="13">
-        <f>GEOMEAN(M29:R29)</f>
+        <f t="shared" ref="M37:M42" si="2">GEOMEAN(M29:R29)</f>
         <v>0.83268317765560429</v>
       </c>
       <c r="O37" s="4" t="s">
@@ -1854,7 +1854,7 @@
         <v>3</v>
       </c>
       <c r="T37" s="13">
-        <f>GEOMEAN(U29:Z29)</f>
+        <f t="shared" ref="T37:T42" si="3">GEOMEAN(U29:Z29)</f>
         <v>1.5130857494229015</v>
       </c>
       <c r="V37" s="4" t="s">
@@ -1870,7 +1870,7 @@
         <v>4</v>
       </c>
       <c r="F38" s="12">
-        <f>GEOMEAN(E30:J30)</f>
+        <f t="shared" si="1"/>
         <v>1.4677992676220697</v>
       </c>
       <c r="H38" s="10" t="s">
@@ -1884,7 +1884,7 @@
         <v>4</v>
       </c>
       <c r="M38" s="13">
-        <f>GEOMEAN(M30:R30)</f>
+        <f t="shared" si="2"/>
         <v>0.45026666156746864</v>
       </c>
       <c r="O38" s="4" t="s">
@@ -1898,7 +1898,7 @@
         <v>4</v>
       </c>
       <c r="T38" s="13">
-        <f>GEOMEAN(U30:Z30)</f>
+        <f t="shared" si="3"/>
         <v>2.4928828716784346</v>
       </c>
       <c r="V38" s="4" t="s">
@@ -1914,7 +1914,7 @@
         <v>5</v>
       </c>
       <c r="F39" s="12">
-        <f>GEOMEAN(E31:J31)</f>
+        <f t="shared" si="1"/>
         <v>0.27329485745122628</v>
       </c>
       <c r="H39" s="10" t="s">
@@ -1928,7 +1928,7 @@
         <v>5</v>
       </c>
       <c r="M39" s="13">
-        <f>GEOMEAN(M31:R31)</f>
+        <f t="shared" si="2"/>
         <v>1.4422495703074083</v>
       </c>
       <c r="O39" s="4" t="s">
@@ -1942,7 +1942,7 @@
         <v>5</v>
       </c>
       <c r="T39" s="13">
-        <f>GEOMEAN(U31:Z31)</f>
+        <f t="shared" si="3"/>
         <v>1.5130857494229015</v>
       </c>
       <c r="V39" s="4" t="s">
@@ -1958,7 +1958,7 @@
         <v>12</v>
       </c>
       <c r="F40" s="12">
-        <f>GEOMEAN(E32:J32)</f>
+        <f t="shared" si="1"/>
         <v>2.4494897427831779</v>
       </c>
       <c r="H40" s="10" t="s">
@@ -1972,7 +1972,7 @@
         <v>12</v>
       </c>
       <c r="M40" s="13">
-        <f>GEOMEAN(M32:R32)</f>
+        <f t="shared" si="2"/>
         <v>0.45026666156746864</v>
       </c>
       <c r="O40" s="4" t="s">
@@ -1986,7 +1986,7 @@
         <v>12</v>
       </c>
       <c r="T40" s="13">
-        <f>GEOMEAN(U32:Z32)</f>
+        <f t="shared" si="3"/>
         <v>0.35737688611920448</v>
       </c>
       <c r="V40" s="4" t="s">
@@ -2002,7 +2002,7 @@
         <v>13</v>
       </c>
       <c r="F41" s="12">
-        <f>GEOMEAN(E33:J33)</f>
+        <f t="shared" si="1"/>
         <v>1.4677992676220697</v>
       </c>
       <c r="H41" s="10" t="s">
@@ -2016,7 +2016,7 @@
         <v>13</v>
       </c>
       <c r="M41" s="13">
-        <f>GEOMEAN(M33:R33)</f>
+        <f t="shared" si="2"/>
         <v>2.5873402367724454</v>
       </c>
       <c r="O41" s="4" t="s">
@@ -2030,7 +2030,7 @@
         <v>13</v>
       </c>
       <c r="T41" s="13">
-        <f>GEOMEAN(U33:Z33)</f>
+        <f t="shared" si="3"/>
         <v>0.55032120814910446</v>
       </c>
       <c r="V41" s="4" t="s">
@@ -2046,7 +2046,7 @@
         <v>14</v>
       </c>
       <c r="F42" s="12">
-        <f>GEOMEAN(E34:J34)</f>
+        <f t="shared" si="1"/>
         <v>0.83268317765560429</v>
       </c>
       <c r="H42" s="10" t="s">
@@ -2060,7 +2060,7 @@
         <v>14</v>
       </c>
       <c r="M42" s="13">
-        <f>GEOMEAN(M34:R34)</f>
+        <f t="shared" si="2"/>
         <v>1.5874010519681994</v>
       </c>
       <c r="O42" s="4" t="s">
@@ -2074,7 +2074,7 @@
         <v>14</v>
       </c>
       <c r="T42" s="13">
-        <f>GEOMEAN(U34:Z34)</f>
+        <f t="shared" si="3"/>
         <v>0.89089871814033927</v>
       </c>
       <c r="V42" s="4" t="s">
@@ -2109,259 +2109,265 @@
       </c>
     </row>
     <row r="44" spans="4:32" x14ac:dyDescent="0.35">
-      <c r="I44" s="47">
+      <c r="I44" s="38">
         <f>SUM(I37:I42)</f>
         <v>1</v>
       </c>
     </row>
     <row r="48" spans="4:32" x14ac:dyDescent="0.35">
-      <c r="E48" s="46" t="s">
+      <c r="E48" s="37" t="s">
         <v>41</v>
       </c>
-      <c r="F48" s="46"/>
-      <c r="L48" s="29" t="s">
+      <c r="F48" s="37"/>
+      <c r="L48" s="39" t="s">
         <v>41</v>
       </c>
-      <c r="M48" s="29"/>
-      <c r="T48" s="29" t="s">
+      <c r="M48" s="39"/>
+      <c r="T48" s="39" t="s">
         <v>41</v>
       </c>
-      <c r="U48" s="29"/>
+      <c r="U48" s="39"/>
     </row>
     <row r="49" spans="5:21" x14ac:dyDescent="0.35">
-      <c r="E49" s="30" t="s">
+      <c r="E49" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="F49" s="31">
+      <c r="F49" s="24">
         <f>SUM(E29:E34)</f>
         <v>9.25</v>
       </c>
-      <c r="L49" s="30" t="s">
+      <c r="L49" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="M49" s="31">
+      <c r="M49" s="24">
         <f>SUM(M29:M34)</f>
         <v>9</v>
       </c>
-      <c r="T49" s="30" t="s">
+      <c r="T49" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="U49" s="31">
+      <c r="U49" s="24">
         <f>SUM(U29:U34)</f>
         <v>5.083333333333333</v>
       </c>
     </row>
     <row r="50" spans="5:21" x14ac:dyDescent="0.35">
-      <c r="E50" s="30" t="s">
+      <c r="E50" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="F50" s="31">
+      <c r="F50" s="24">
         <f>SUM(F29:F34)</f>
         <v>5.2</v>
       </c>
-      <c r="L50" s="30" t="s">
+      <c r="L50" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="M50" s="31">
+      <c r="M50" s="24">
         <f>SUM(N29:N34)</f>
         <v>16</v>
       </c>
-      <c r="T50" s="30" t="s">
+      <c r="T50" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="U50" s="31">
+      <c r="U50" s="24">
         <f>SUM(V29:V34)</f>
         <v>2.7833333333333337</v>
       </c>
     </row>
     <row r="51" spans="5:21" x14ac:dyDescent="0.35">
-      <c r="E51" s="30" t="s">
+      <c r="E51" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="F51" s="31">
+      <c r="F51" s="24">
         <f>SUM(G29:G34)</f>
         <v>25</v>
       </c>
-      <c r="L51" s="30" t="s">
+      <c r="L51" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="M51" s="31">
+      <c r="M51" s="24">
         <f>SUM(O29:O34)</f>
         <v>5.1666666666666661</v>
       </c>
-      <c r="T51" s="30" t="s">
+      <c r="T51" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="U51" s="31">
+      <c r="U51" s="24">
         <f>SUM(W29:W34)</f>
         <v>5.083333333333333</v>
       </c>
     </row>
     <row r="52" spans="5:21" x14ac:dyDescent="0.35">
-      <c r="E52" s="30" t="s">
+      <c r="E52" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="F52" s="31">
+      <c r="F52" s="24">
         <f>SUM(H29:H34)</f>
         <v>2.8333333333333335</v>
       </c>
-      <c r="L52" s="30" t="s">
+      <c r="L52" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="M52" s="31">
+      <c r="M52" s="24">
         <f>SUM(P29:P34)</f>
         <v>16</v>
       </c>
-      <c r="T52" s="30" t="s">
+      <c r="T52" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="U52" s="31">
+      <c r="U52" s="24">
         <f>SUM(X29:X34)</f>
         <v>19</v>
       </c>
     </row>
     <row r="53" spans="5:21" x14ac:dyDescent="0.35">
-      <c r="E53" s="30" t="s">
+      <c r="E53" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="F53" s="31">
+      <c r="F53" s="24">
         <f>SUM(I29:I34)</f>
         <v>5.2</v>
       </c>
-      <c r="L53" s="30" t="s">
+      <c r="L53" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="M53" s="31">
+      <c r="M53" s="24">
         <f>SUM(Q29:Q34)</f>
         <v>2.7333333333333334</v>
       </c>
-      <c r="T53" s="30" t="s">
+      <c r="T53" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="U53" s="31">
+      <c r="U53" s="24">
         <f>SUM(Y29:Y34)</f>
         <v>13.5</v>
       </c>
     </row>
     <row r="54" spans="5:21" x14ac:dyDescent="0.35">
-      <c r="E54" s="30" t="s">
+      <c r="E54" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="F54" s="31">
+      <c r="F54" s="24">
         <f>SUM(J29:J34)</f>
         <v>9.25</v>
       </c>
-      <c r="L54" s="30" t="s">
+      <c r="L54" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="M54" s="31">
+      <c r="M54" s="24">
         <f>SUM(R29:R34)</f>
         <v>5</v>
       </c>
-      <c r="T54" s="30" t="s">
+      <c r="T54" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="U54" s="31">
+      <c r="U54" s="24">
         <f>SUM(Z29:Z34)</f>
         <v>8.8333333333333321</v>
       </c>
     </row>
     <row r="61" spans="5:21" x14ac:dyDescent="0.35">
-      <c r="E61" s="22" t="s">
+      <c r="E61" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="F61" s="23">
+      <c r="F61" s="17">
         <f>F49*I37+F50*I38+F51*I39+F52*I40+F53*I41+F54*I42</f>
         <v>6.0682500951124316</v>
       </c>
-      <c r="L61" s="22" t="s">
+      <c r="L61" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="M61" s="23">
+      <c r="M61" s="17">
         <f>M49*P37+M50*P38+M51*P39+M52*P40+M53*P41+M54*P42</f>
         <v>6.8067830486833092</v>
       </c>
-      <c r="T61" s="22" t="s">
+      <c r="T61" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="U61" s="23">
+      <c r="U61" s="17">
         <f>U49*W37+U50*W38+U51*W39+U52*W40+U53*W41+U54*W42</f>
         <v>7.6509887680429545</v>
       </c>
     </row>
     <row r="63" spans="5:21" x14ac:dyDescent="0.35">
-      <c r="E63" s="24" t="s">
+      <c r="E63" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="F63" s="23">
+      <c r="F63" s="17">
         <f>(F61-3)/(3-1)</f>
         <v>1.5341250475562158</v>
       </c>
-      <c r="L63" s="24" t="s">
+      <c r="L63" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="M63" s="23">
+      <c r="M63" s="17">
         <f>(M61-3)/(3-1)</f>
         <v>1.9033915243416546</v>
       </c>
-      <c r="T63" s="24" t="s">
+      <c r="T63" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="U63" s="23">
+      <c r="U63" s="17">
         <f>(U61-3)/(3-1)</f>
         <v>2.3254943840214772</v>
       </c>
     </row>
     <row r="65" spans="5:21" x14ac:dyDescent="0.35">
-      <c r="E65" s="24" t="s">
+      <c r="E65" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="F65" s="23">
+      <c r="F65" s="17">
         <v>1.1200000000000001</v>
       </c>
-      <c r="L65" s="24" t="s">
+      <c r="L65" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="M65" s="23">
+      <c r="M65" s="17">
         <v>1.1200000000000001</v>
       </c>
-      <c r="T65" s="24" t="s">
+      <c r="T65" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="U65" s="23">
+      <c r="U65" s="17">
         <v>1.1200000000000001</v>
       </c>
     </row>
     <row r="67" spans="5:21" x14ac:dyDescent="0.35">
-      <c r="E67" s="24" t="s">
+      <c r="E67" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="F67" s="23">
+      <c r="F67" s="17">
         <f>F63/F65</f>
         <v>1.369754506746621</v>
       </c>
-      <c r="L67" s="24" t="s">
+      <c r="L67" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="M67" s="23">
+      <c r="M67" s="17">
         <f>M63/M65</f>
         <v>1.6994567181621913</v>
       </c>
-      <c r="T67" s="24" t="s">
+      <c r="T67" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="U67" s="23">
+      <c r="U67" s="17">
         <f>U63/U65</f>
         <v>2.0763342714477475</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="T48:U48"/>
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="P13:Q13"/>
-    <mergeCell ref="R13:S13"/>
-    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="E27:J27"/>
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="H36:I36"/>
+    <mergeCell ref="AB28:AC28"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="J13:K13"/>
     <mergeCell ref="L48:M48"/>
     <mergeCell ref="L27:Q27"/>
     <mergeCell ref="AE28:AF28"/>
@@ -2369,17 +2375,11 @@
     <mergeCell ref="O36:P36"/>
     <mergeCell ref="S36:T36"/>
     <mergeCell ref="V36:W36"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="E27:J27"/>
-    <mergeCell ref="E36:F36"/>
-    <mergeCell ref="H36:I36"/>
-    <mergeCell ref="AB28:AC28"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="T48:U48"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="P13:Q13"/>
+    <mergeCell ref="R13:S13"/>
+    <mergeCell ref="R6:S6"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
